--- a/data/trans_camb/IP21B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,0</t>
+          <t>0,0; 29,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 0,0</t>
+          <t>-20,91; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 0,0</t>
+          <t>-22,15; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 0,0</t>
+          <t>-22,2; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 15,53</t>
+          <t>-2,14; 15,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 0,0</t>
+          <t>-10,5; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 0,0</t>
+          <t>-10,44; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-61,91; 29,27</t>
+          <t>-55,24; 34,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 55,76</t>
+          <t>-36,66; 56,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,19; 62,56</t>
+          <t>-47,82; 55,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 36,41</t>
+          <t>-24,85; 38,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 65,42</t>
+          <t>-35,17; 64,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 40,47</t>
+          <t>-42,99; 41,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 27,36</t>
+          <t>-23,37; 26,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 48,98</t>
+          <t>-14,98; 47,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 36,69</t>
+          <t>-31,18; 33,16</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,78; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,69; —</t>
+          <t>-66,23; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,25; 345,71</t>
+          <t>-55,04; 348,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 471,58</t>
+          <t>-100,0; 653,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,51; 230,07</t>
+          <t>-54,03; 175,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 306,02</t>
+          <t>-39,37; 371,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-78,45; 275,95</t>
+          <t>-78,17; 241,21</t>
         </is>
       </c>
     </row>
@@ -1114,42 +1114,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-81,63; 56,26</t>
+          <t>-81,61; 55,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,78</t>
+          <t>-100,0; 42,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 0,0</t>
+          <t>-49,0; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 72,73</t>
+          <t>-20,4; 72,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 86,6</t>
+          <t>-27,6; 90,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,13; -7,49</t>
+          <t>-58,37; -7,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 46,75</t>
+          <t>-29,64; 47,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 55,82</t>
+          <t>-35,0; 62,04</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,7; 623,35</t>
+          <t>-62,01; 620,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,52</t>
+          <t>0,0; 61,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,18</t>
+          <t>0,0; 53,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,81</t>
+          <t>0,0; 50,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,35</t>
+          <t>0,0; 43,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,12</t>
+          <t>0,0; 75,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 20,88</t>
+          <t>-7,78; 21,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 30,65</t>
+          <t>-3,51; 30,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 47,15</t>
+          <t>-5,67; 41,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 21,64</t>
+          <t>-8,2; 20,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 29,06</t>
+          <t>-6,48; 29,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 44,01</t>
+          <t>-7,64; 38,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 16,49</t>
+          <t>-4,42; 16,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 23,43</t>
+          <t>-0,94; 24,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 32,18</t>
+          <t>0,4; 33,25</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 625,71</t>
+          <t>-61,76; 629,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 906,0</t>
+          <t>-41,59; 775,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,6; 462,12</t>
+          <t>-47,05; 352,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 449,94</t>
+          <t>-46,07; 475,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 824,56</t>
+          <t>-62,86; 651,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 260,46</t>
+          <t>-31,17; 247,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 356,3</t>
+          <t>-11,46; 360,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 477,27</t>
+          <t>-9,88; 472,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,53</t>
+          <t>0,0; 31,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 0,0</t>
+          <t>-21,98; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 0,0</t>
+          <t>-21,69; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 0,0</t>
+          <t>-21,76; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 15,42</t>
+          <t>-2,13; 16,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 0,0</t>
+          <t>-10,48; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 0,0</t>
+          <t>-9,93; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-55,24; 34,89</t>
+          <t>-53,23; 34,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 56,9</t>
+          <t>-39,01; 57,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 55,66</t>
+          <t>-51,16; 56,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 38,47</t>
+          <t>-27,53; 39,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 64,71</t>
+          <t>-36,02; 63,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,99; 41,5</t>
+          <t>-43,04; 41,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 26,36</t>
+          <t>-25,3; 24,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 47,1</t>
+          <t>-18,03; 46,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 33,16</t>
+          <t>-30,7; 36,13</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,78; —</t>
+          <t>-86,19; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,23; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,04; 348,26</t>
+          <t>-61,03; 451,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 653,23</t>
+          <t>-100,0; 512,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,03; 175,87</t>
+          <t>-57,14; 157,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 371,19</t>
+          <t>-42,02; 371,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-78,17; 241,21</t>
+          <t>-82,24; 290,88</t>
         </is>
       </c>
     </row>
@@ -1114,42 +1114,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 55,05</t>
+          <t>-81,63; 53,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,49</t>
+          <t>-100,0; 61,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 0,0</t>
+          <t>-56,89; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 72,29</t>
+          <t>-15,13; 71,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 90,65</t>
+          <t>-28,2; 86,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,37; -7,62</t>
+          <t>-66,63; -7,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 47,39</t>
+          <t>-29,68; 46,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 62,04</t>
+          <t>-36,66; 55,94</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 620,71</t>
+          <t>-69,53; 603,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,47</t>
+          <t>0,0; 61,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,57</t>
+          <t>0,0; 59,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,63</t>
+          <t>0,0; 48,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,24</t>
+          <t>0,0; 35,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,14</t>
+          <t>0,0; 75,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 21,33</t>
+          <t>-9,02; 19,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 30,35</t>
+          <t>-3,29; 31,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 41,03</t>
+          <t>-6,28; 45,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 20,11</t>
+          <t>-7,6; 20,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 29,33</t>
+          <t>-7,92; 26,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 38,87</t>
+          <t>-7,43; 41,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 16,19</t>
+          <t>-4,8; 15,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 24,29</t>
+          <t>-1,65; 24,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 33,25</t>
+          <t>-2,7; 34,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 629,33</t>
+          <t>-66,93; 562,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 775,36</t>
+          <t>-37,11; 952,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1532,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 352,22</t>
+          <t>-46,4; 344,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 475,78</t>
+          <t>-56,42; 418,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 651,79</t>
+          <t>-49,91; 645,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 247,41</t>
+          <t>-34,52; 237,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 360,51</t>
+          <t>-15,38; 346,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 472,79</t>
+          <t>-27,59; 447,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,39</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,89</t>
+          <t>-24,09; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,85; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,84; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 0,0</t>
+          <t>0,0; 29,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 16,11</t>
+          <t>-3,35; 15,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 0,0</t>
+          <t>-10,49; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 0,0</t>
+          <t>-8,9; 0,0</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,21</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-9,22</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-5,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,66</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,47</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,73</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,21</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,71</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>1,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-53,23; 34,06</t>
+          <t>-28,94; 36,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 57,54</t>
+          <t>-33,19; 65,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-51,16; 56,05</t>
+          <t>-43,19; 41,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 39,21</t>
+          <t>-61,91; 29,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,02; 63,7</t>
+          <t>-39,51; 55,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 41,79</t>
+          <t>-45,25; 65,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 24,72</t>
+          <t>-25,72; 27,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 46,0</t>
+          <t>-15,64; 48,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 36,13</t>
+          <t>-31,32; 41,5</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-31,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-17,74%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>41,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,59%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-33,42%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2,82%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,19; —</t>
+          <t>-58,25; 345,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 471,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 451,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 512,38</t>
+          <t>-69,69; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-57,14; 157,65</t>
+          <t>-56,51; 230,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 371,17</t>
+          <t>-47,3; 306,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,24; 290,88</t>
+          <t>-78,37; 308,93</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-13,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27,93</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-60,26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-23,45</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-31,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-13,51</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>27,93</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,82</t>
+          <t>-28,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>3,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>-56,01; 0,0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>-14,38; 72,73</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>-27,7; 86,6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>-100,0; 0,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-81,63; 53,77</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 61,73</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-56,89; 0,0</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 71,72</t>
+          <t>-81,63; 56,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 86,59</t>
+          <t>-100,0; 70,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-66,63; -7,85</t>
+          <t>-58,13; -7,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 46,71</t>
+          <t>-27,36; 46,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 55,94</t>
+          <t>-35,73; 52,65</t>
         </is>
       </c>
     </row>
@@ -1167,34 +1167,34 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>206,8%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>125,25%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>-38,92%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-52,47%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-47,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>206,8%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>146,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>44,69%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,53; 603,31</t>
+          <t>-66,7; 623,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22,58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14,04</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45,5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22,58</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,04</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,84</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>18,06</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>32,88</t>
+          <t>34,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 59,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,95</t>
+          <t>0,0; 48,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,91</t>
+          <t>0,0; 44,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,95</t>
+          <t>0,0; 79,49</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,96</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14,21</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,81</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>12,79</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14,62</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,96</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>16,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,95</t>
+          <t>15,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 19,5</t>
+          <t>-7,8; 21,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 31,01</t>
+          <t>-8,19; 29,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 45,9</t>
+          <t>-6,51; 45,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 20,09</t>
+          <t>-7,84; 20,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 26,83</t>
+          <t>-2,99; 30,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 41,92</t>
+          <t>-4,35; 49,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 15,74</t>
+          <t>-4,16; 16,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 24,08</t>
+          <t>-1,7; 23,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 34,41</t>
+          <t>-0,76; 34,46</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>115,78%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>59,82%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>131,59%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>150,45%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>72,98%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>109,29%</t>
+          <t>174,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>124,94%</t>
+          <t>137,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 562,02</t>
+          <t>-45,6; 462,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 952,86</t>
+          <t>-50,28; 449,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1532,13</t>
+          <t>-47,43; 887,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 344,24</t>
+          <t>-65,48; 625,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 418,45</t>
+          <t>-36,55; 906,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,91; 645,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 237,55</t>
+          <t>-29,11; 260,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 346,3</t>
+          <t>-17,47; 356,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 447,08</t>
+          <t>-6,84; 527,77</t>
         </is>
       </c>
     </row>
